--- a/EdenCampus_PhD/04_results/tables/sensitivity_analysis.xlsx
+++ b/EdenCampus_PhD/04_results/tables/sensitivity_analysis.xlsx
@@ -462,22 +462,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>114.5</v>
+        <v>113.8</v>
       </c>
       <c r="D2" t="n">
-        <v>38.7</v>
+        <v>39.2</v>
       </c>
       <c r="E2" t="n">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="F2" t="n">
-        <v>32071.9</v>
+        <v>31.9</v>
       </c>
       <c r="G2" t="n">
-        <v>656.7</v>
+        <v>652.1</v>
       </c>
     </row>
     <row r="3">
@@ -487,22 +487,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>107.5</v>
       </c>
       <c r="D3" t="n">
-        <v>46.9</v>
+        <v>42.8</v>
       </c>
       <c r="E3" t="n">
-        <v>20.2</v>
+        <v>18.5</v>
       </c>
       <c r="F3" t="n">
-        <v>27989.7</v>
+        <v>30.1</v>
       </c>
       <c r="G3" t="n">
-        <v>634.3</v>
+        <v>644.8</v>
       </c>
     </row>
     <row r="4">
@@ -512,22 +512,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67.8</v>
+        <v>69.2</v>
       </c>
       <c r="C4" t="n">
-        <v>118.1</v>
+        <v>117.2</v>
       </c>
       <c r="D4" t="n">
-        <v>36.7</v>
+        <v>37.4</v>
       </c>
       <c r="E4" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="F4" t="n">
-        <v>33081.4</v>
+        <v>32.8</v>
       </c>
       <c r="G4" t="n">
-        <v>667.3</v>
+        <v>667.8</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>78.3</v>
       </c>
       <c r="C5" t="n">
-        <v>107.9</v>
+        <v>108.4</v>
       </c>
       <c r="D5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="E5" t="n">
         <v>18.3</v>
       </c>
       <c r="F5" t="n">
-        <v>30217.2</v>
+        <v>30.3</v>
       </c>
       <c r="G5" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
   </sheetData>
@@ -614,19 +614,19 @@
         <v>78.3</v>
       </c>
       <c r="C2" t="n">
-        <v>107.9</v>
+        <v>108.4</v>
       </c>
       <c r="D2" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="E2" t="n">
         <v>18.3</v>
       </c>
       <c r="F2" t="n">
-        <v>19425.3</v>
+        <v>19.5</v>
       </c>
       <c r="G2" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="3">
@@ -637,19 +637,19 @@
         <v>78.3</v>
       </c>
       <c r="C3" t="n">
-        <v>107.9</v>
+        <v>108.4</v>
       </c>
       <c r="D3" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="E3" t="n">
         <v>18.3</v>
       </c>
       <c r="F3" t="n">
-        <v>23742.1</v>
+        <v>23.8</v>
       </c>
       <c r="G3" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="4">
@@ -660,19 +660,19 @@
         <v>78.3</v>
       </c>
       <c r="C4" t="n">
-        <v>107.9</v>
+        <v>108.4</v>
       </c>
       <c r="D4" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="E4" t="n">
         <v>18.3</v>
       </c>
       <c r="F4" t="n">
-        <v>28058.8</v>
+        <v>28.2</v>
       </c>
       <c r="G4" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="5">
@@ -683,19 +683,19 @@
         <v>78.3</v>
       </c>
       <c r="C5" t="n">
-        <v>107.9</v>
+        <v>108.4</v>
       </c>
       <c r="D5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="E5" t="n">
         <v>18.3</v>
       </c>
       <c r="F5" t="n">
-        <v>30217.2</v>
+        <v>30.3</v>
       </c>
       <c r="G5" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="6">
@@ -706,19 +706,19 @@
         <v>78.3</v>
       </c>
       <c r="C6" t="n">
-        <v>107.9</v>
+        <v>108.4</v>
       </c>
       <c r="D6" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="E6" t="n">
         <v>18.3</v>
       </c>
       <c r="F6" t="n">
-        <v>32375.5</v>
+        <v>32.5</v>
       </c>
       <c r="G6" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="7">
@@ -729,19 +729,19 @@
         <v>78.3</v>
       </c>
       <c r="C7" t="n">
-        <v>107.9</v>
+        <v>108.4</v>
       </c>
       <c r="D7" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="E7" t="n">
         <v>18.3</v>
       </c>
       <c r="F7" t="n">
-        <v>36692.3</v>
+        <v>36.8</v>
       </c>
       <c r="G7" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="8">
@@ -752,19 +752,19 @@
         <v>78.3</v>
       </c>
       <c r="C8" t="n">
-        <v>107.9</v>
+        <v>108.4</v>
       </c>
       <c r="D8" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="E8" t="n">
         <v>18.3</v>
       </c>
       <c r="F8" t="n">
-        <v>41009</v>
+        <v>41.2</v>
       </c>
       <c r="G8" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
   </sheetData>
@@ -829,16 +829,16 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="E2" t="n">
         <v>15.4</v>
       </c>
       <c r="F2" t="n">
-        <v>33303.8</v>
+        <v>33.4</v>
       </c>
       <c r="G2" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="3">
@@ -858,10 +858,10 @@
         <v>16.1</v>
       </c>
       <c r="F3" t="n">
-        <v>32590.8</v>
+        <v>32.7</v>
       </c>
       <c r="G3" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="4">
@@ -881,10 +881,10 @@
         <v>17.3</v>
       </c>
       <c r="F4" t="n">
-        <v>31228.7</v>
+        <v>31.3</v>
       </c>
       <c r="G4" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="5">
@@ -904,10 +904,10 @@
         <v>17.3</v>
       </c>
       <c r="F5" t="n">
-        <v>31228.6</v>
+        <v>31.3</v>
       </c>
       <c r="G5" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="6">
@@ -921,16 +921,16 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="E6" t="n">
         <v>18.3</v>
       </c>
       <c r="F6" t="n">
-        <v>30217.2</v>
+        <v>30.3</v>
       </c>
       <c r="G6" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="7">
@@ -944,16 +944,16 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="E7" t="n">
         <v>18.7</v>
       </c>
       <c r="F7" t="n">
-        <v>29687.8</v>
+        <v>29.8</v>
       </c>
       <c r="G7" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="8">
@@ -967,16 +967,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="E8" t="n">
         <v>18.7</v>
       </c>
       <c r="F8" t="n">
-        <v>29687.8</v>
+        <v>29.8</v>
       </c>
       <c r="G8" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
     <row r="9">
@@ -990,16 +990,16 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="E9" t="n">
         <v>19.2</v>
       </c>
       <c r="F9" t="n">
-        <v>29159.7</v>
+        <v>29.3</v>
       </c>
       <c r="G9" t="n">
-        <v>652.2</v>
+        <v>652.7</v>
       </c>
     </row>
   </sheetData>
